--- a/events/LaSeu_2016_WC/LaSeu_2016_WC_start.xlsx
+++ b/events/LaSeu_2016_WC/LaSeu_2016_WC_start.xlsx
@@ -2438,7 +2438,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>LIB</t>
+          <t>LBN</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>LIB</t>
+          <t>LBN</t>
         </is>
       </c>
       <c r="J219" t="n">
